--- a/Question 2/Specs.xlsx
+++ b/Question 2/Specs.xlsx
@@ -10,14 +10,14 @@
     <sheet name="GRADRATESSPECS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="GRADRATESSPECS">'GRADRATESSPECS'!$A$1:$H$17</definedName>
+    <definedName name="GRADRATESSPECS">'GRADRATESSPECS'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Member</t>
   </si>
@@ -97,7 +97,7 @@
     <t>Hispanic total</t>
   </si>
   <si>
-    <t>White_Toal</t>
+    <t>White_Total</t>
   </si>
   <si>
     <t>White total</t>
@@ -143,6 +143,15 @@
   </si>
   <si>
     <t>Out_State_Tution</t>
+  </si>
+  <si>
+    <t>total_staff</t>
+  </si>
+  <si>
+    <t>Instructional staff on 9-month contract-total</t>
+  </si>
+  <si>
+    <t>Student_Faculty_Ratio</t>
   </si>
 </sst>
 </file>
@@ -927,6 +936,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>

--- a/Question 2/Specs.xlsx
+++ b/Question 2/Specs.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Member</t>
   </si>
@@ -79,43 +79,25 @@
     <t>Total women</t>
   </si>
   <si>
-    <t>Asian_Total</t>
-  </si>
-  <si>
-    <t>Asian total</t>
-  </si>
-  <si>
-    <t>African_American_Total</t>
-  </si>
-  <si>
-    <t>Black or African American total</t>
-  </si>
-  <si>
-    <t>Hispanic_Total</t>
-  </si>
-  <si>
-    <t>Hispanic total</t>
-  </si>
-  <si>
-    <t>White_Total</t>
-  </si>
-  <si>
-    <t>White total</t>
+    <t>Asian</t>
+  </si>
+  <si>
+    <t>African_American</t>
+  </si>
+  <si>
+    <t>Hispanic</t>
+  </si>
+  <si>
+    <t>White</t>
   </si>
   <si>
     <t>Multi_Race</t>
   </si>
   <si>
-    <t>Two or more races total</t>
-  </si>
-  <si>
     <t>Race_Other</t>
   </si>
   <si>
     <t>Race_Unknown</t>
-  </si>
-  <si>
-    <t>Race/ethnicity unknown total</t>
   </si>
   <si>
     <t>control</t>
@@ -670,10 +652,10 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -684,7 +666,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -696,10 +678,10 @@
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -710,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>
@@ -722,10 +704,10 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -736,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>1</v>
@@ -748,10 +730,10 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -762,7 +744,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>1</v>
@@ -774,10 +756,10 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -788,7 +770,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>1</v>
@@ -814,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
         <v>1</v>
@@ -826,10 +808,10 @@
         <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -840,7 +822,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
         <v>1</v>
@@ -849,13 +831,13 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -866,7 +848,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
         <v>1</v>
@@ -875,13 +857,13 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -892,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
         <v>1</v>
@@ -918,7 +900,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
         <v>1</v>
@@ -944,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
         <v>1</v>
@@ -959,7 +941,7 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -970,7 +952,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
         <v>1</v>
